--- a/excel_routes/route_HMB_ELQ_threats.xlsx
+++ b/excel_routes/route_HMB_ELQ_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89566598-A06C-4F8F-A125-38A06B49BDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969C4F71-880D-4D19-B737-66B78614F744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="27">
   <si>
     <t>Date</t>
   </si>
@@ -79,6 +79,12 @@
   </si>
   <si>
     <t>05-AUG-26</t>
+  </si>
+  <si>
+    <t>Nile Air NP-315</t>
+  </si>
+  <si>
+    <t>12-AUG-26</t>
   </si>
   <si>
     <t>19-AUG-26</t>
@@ -496,7 +502,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -557,13 +563,13 @@
         <v>13</v>
       </c>
       <c r="D2" s="2">
-        <v>14758</v>
+        <v>15208</v>
       </c>
       <c r="E2" s="2">
-        <v>19632</v>
+        <v>19631</v>
       </c>
       <c r="F2" s="2">
-        <v>-4874</v>
+        <v>-4423</v>
       </c>
       <c r="G2" s="2">
         <v>30</v>
@@ -595,10 +601,10 @@
         <v>15208</v>
       </c>
       <c r="E3" s="2">
-        <v>19632</v>
+        <v>19631</v>
       </c>
       <c r="F3" s="2">
-        <v>-4424</v>
+        <v>-4423</v>
       </c>
       <c r="G3" s="2">
         <v>30</v>
@@ -624,16 +630,16 @@
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2">
-        <v>10607</v>
+        <v>10648</v>
       </c>
       <c r="E4" s="2">
         <v>13638</v>
       </c>
       <c r="F4" s="2">
-        <v>-3031</v>
+        <v>-2990</v>
       </c>
       <c r="G4" s="2">
         <v>30</v>
@@ -653,13 +659,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2">
         <v>10648</v>
@@ -688,22 +694,22 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2">
-        <v>11891</v>
+        <v>10648</v>
       </c>
       <c r="E6" s="2">
-        <v>14635</v>
+        <v>13638</v>
       </c>
       <c r="F6" s="2">
-        <v>-2744</v>
+        <v>-2990</v>
       </c>
       <c r="G6" s="2">
         <v>30</v>
@@ -723,34 +729,34 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D7" s="2">
-        <v>8341</v>
+        <v>12000</v>
       </c>
       <c r="E7" s="2">
-        <v>16137</v>
+        <v>16136</v>
       </c>
       <c r="F7" s="2">
-        <v>-7796</v>
+        <v>-4136</v>
       </c>
       <c r="G7" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2">
         <v>30</v>
       </c>
       <c r="I7" s="2">
-        <v>10</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>15</v>
@@ -758,31 +764,31 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2">
-        <v>10225</v>
+        <v>13392</v>
       </c>
       <c r="E8" s="2">
-        <v>16137</v>
+        <v>16136</v>
       </c>
       <c r="F8" s="2">
-        <v>-5912</v>
+        <v>-2744</v>
       </c>
       <c r="G8" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2">
         <v>30</v>
       </c>
       <c r="I8" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>14</v>
@@ -793,34 +799,34 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2">
-        <v>10607</v>
+        <v>8813</v>
       </c>
       <c r="E9" s="2">
-        <v>16137</v>
+        <v>16136</v>
       </c>
       <c r="F9" s="2">
-        <v>-5530</v>
+        <v>-7323</v>
       </c>
       <c r="G9" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2">
         <v>30</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>15</v>
@@ -828,34 +834,34 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="2">
+        <v>9870</v>
+      </c>
+      <c r="E10" s="2">
+        <v>16136</v>
+      </c>
+      <c r="F10" s="2">
+        <v>-6266</v>
+      </c>
+      <c r="G10" s="2">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="2">
-        <v>8341</v>
-      </c>
-      <c r="E10" s="2">
-        <v>16137</v>
-      </c>
-      <c r="F10" s="2">
-        <v>-7796</v>
-      </c>
-      <c r="G10" s="2">
-        <v>20</v>
-      </c>
-      <c r="H10" s="2">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2">
-        <v>10</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>15</v>
@@ -863,34 +869,34 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="2">
+        <v>10225</v>
+      </c>
+      <c r="E11" s="2">
+        <v>16136</v>
+      </c>
+      <c r="F11" s="2">
+        <v>-5911</v>
+      </c>
+      <c r="G11" s="2">
         <v>23</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="2">
-        <v>8914</v>
-      </c>
-      <c r="E11" s="2">
-        <v>16137</v>
-      </c>
-      <c r="F11" s="2">
-        <v>-7223</v>
-      </c>
-      <c r="G11" s="2">
-        <v>30</v>
-      </c>
       <c r="H11" s="2">
         <v>30</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>21</v>
+        <v>7</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>15</v>
@@ -898,34 +904,34 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="2">
+        <v>8303</v>
+      </c>
+      <c r="E12" s="2">
+        <v>16136</v>
+      </c>
+      <c r="F12" s="2">
+        <v>-7833</v>
+      </c>
+      <c r="G12" s="2">
+        <v>20</v>
+      </c>
+      <c r="H12" s="2">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2">
+        <v>10</v>
+      </c>
+      <c r="J12" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="2">
-        <v>10130</v>
-      </c>
-      <c r="E12" s="2">
-        <v>16137</v>
-      </c>
-      <c r="F12" s="2">
-        <v>-6007</v>
-      </c>
-      <c r="G12" s="2">
-        <v>30</v>
-      </c>
-      <c r="H12" s="2">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>15</v>
@@ -933,34 +939,34 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D13" s="2">
-        <v>7573</v>
+        <v>8914</v>
       </c>
       <c r="E13" s="2">
-        <v>16137</v>
+        <v>16136</v>
       </c>
       <c r="F13" s="2">
-        <v>-8564</v>
+        <v>-7222</v>
       </c>
       <c r="G13" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2">
         <v>30</v>
       </c>
       <c r="I13" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>15</v>
@@ -968,34 +974,34 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D14" s="2">
-        <v>7631</v>
+        <v>10648</v>
       </c>
       <c r="E14" s="2">
-        <v>16137</v>
+        <v>16136</v>
       </c>
       <c r="F14" s="2">
-        <v>-8506</v>
+        <v>-5488</v>
       </c>
       <c r="G14" s="2">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="H14" s="2">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2">
-        <v>7</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>15</v>
@@ -1003,36 +1009,106 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="2">
+        <v>7538</v>
+      </c>
+      <c r="E15" s="2">
+        <v>16136</v>
+      </c>
+      <c r="F15" s="2">
+        <v>-8598</v>
+      </c>
+      <c r="G15" s="2">
+        <v>20</v>
+      </c>
+      <c r="H15" s="2">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2">
+        <v>10</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D16" s="2">
+        <v>7631</v>
+      </c>
+      <c r="E16" s="2">
+        <v>16136</v>
+      </c>
+      <c r="F16" s="2">
+        <v>-8505</v>
+      </c>
+      <c r="G16" s="2">
+        <v>23</v>
+      </c>
+      <c r="H16" s="2">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D17" s="2">
         <v>8314</v>
       </c>
-      <c r="E15" s="2">
-        <v>16137</v>
-      </c>
-      <c r="F15" s="2">
-        <v>-7823</v>
-      </c>
-      <c r="G15" s="2">
-        <v>30</v>
-      </c>
-      <c r="H15" s="2">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2">
+      <c r="E17" s="2">
+        <v>16136</v>
+      </c>
+      <c r="F17" s="2">
+        <v>-7822</v>
+      </c>
+      <c r="G17" s="2">
+        <v>30</v>
+      </c>
+      <c r="H17" s="2">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2">
         <v>0</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="2" t="s">
+      <c r="J17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>15</v>
       </c>
     </row>
